--- a/excel/Indemo.xlsx
+++ b/excel/Indemo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Indemo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.08.08\Indemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E406AABB-EAB9-4F79-9F0C-F9D035EDD623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6346771D-098A-479F-8F47-E24A9C334441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="33" r:id="rId1"/>
@@ -1044,7 +1044,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1121,10 +1121,16 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1133,16 +1139,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1153,12 +1156,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7202,41 +7199,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35" t="s">
+      <c r="A1" s="38"/>
+      <c r="B1" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="32" t="s">
+      <c r="D1" s="37"/>
+      <c r="E1" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="33"/>
-      <c r="K1" s="38" t="s">
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="35"/>
+      <c r="K1" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="32" t="s">
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="35"/>
+      <c r="Q1" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="19" t="s">
         <v>228</v>
       </c>
@@ -7363,7 +7360,7 @@
       </c>
       <c r="T3" s="6">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.14429696202278133</v>
+        <v>0.12463424801826478</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -10522,7 +10519,7 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="30">
+      <c r="A89" s="4">
         <v>87</v>
       </c>
       <c r="B89" s="23" t="s">
@@ -10725,21 +10722,21 @@
       <c r="B1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -10748,8 +10745,8 @@
       <c r="B2" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -11357,21 +11354,21 @@
       <c r="B1" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -11380,8 +11377,8 @@
       <c r="B2" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -11992,21 +11989,21 @@
       <c r="B1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -12015,8 +12012,8 @@
       <c r="B2" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -12649,21 +12646,21 @@
       <c r="B1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -12672,8 +12669,8 @@
       <c r="B2" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -13313,21 +13310,21 @@
       <c r="B1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -13336,8 +13333,8 @@
       <c r="B2" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -13985,21 +13982,21 @@
       <c r="B1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -14008,8 +14005,8 @@
       <c r="B2" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -14657,21 +14654,21 @@
       <c r="B1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -14680,8 +14677,8 @@
       <c r="B2" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -15324,21 +15321,21 @@
       <c r="B1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -15347,8 +15344,8 @@
       <c r="B2" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -15914,21 +15911,21 @@
       <c r="B1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -15937,8 +15934,8 @@
       <c r="B2" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -16570,21 +16567,21 @@
       <c r="B1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -16593,8 +16590,8 @@
       <c r="B2" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -17249,7 +17246,7 @@
       </c>
       <c r="I2" s="6">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>0.14429696202278133</v>
+        <v>0.12463424801826478</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="5">
@@ -17728,7 +17725,7 @@
       <c r="C28" s="5">
         <v>0</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="4">
         <v>0.31</v>
       </c>
       <c r="K28" s="5">
@@ -18951,7 +18948,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="24">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46295</v>
       </c>
       <c r="B200" s="26"/>
       <c r="C200" s="26"/>
@@ -18994,21 +18991,21 @@
       <c r="B1" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -19017,8 +19014,8 @@
       <c r="B2" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -19650,21 +19647,21 @@
       <c r="B1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -19673,8 +19670,8 @@
       <c r="B2" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -20298,21 +20295,21 @@
       <c r="B1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -20321,8 +20318,8 @@
       <c r="B2" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -20938,21 +20935,21 @@
       <c r="B1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -20961,8 +20958,8 @@
       <c r="B2" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -21570,21 +21567,21 @@
       <c r="B1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -21593,8 +21590,8 @@
       <c r="B2" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -22210,21 +22207,21 @@
       <c r="B1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -22233,8 +22230,8 @@
       <c r="B2" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -22882,21 +22879,21 @@
       <c r="B1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -22905,8 +22902,8 @@
       <c r="B2" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -23514,21 +23511,21 @@
       <c r="B1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -23537,8 +23534,8 @@
       <c r="B2" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -24378,21 +24375,21 @@
       <c r="B1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -24401,8 +24398,8 @@
       <c r="B2" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -25146,21 +25143,21 @@
       <c r="B1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -25169,8 +25166,8 @@
       <c r="B2" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -25898,21 +25895,21 @@
       <c r="B1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -25921,8 +25918,8 @@
       <c r="B2" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -26159,21 +26156,21 @@
       <c r="B1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -26182,8 +26179,8 @@
       <c r="B2" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -26821,21 +26818,21 @@
       <c r="B1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -26844,8 +26841,8 @@
       <c r="B2" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -27565,21 +27562,21 @@
       <c r="B1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -27588,8 +27585,8 @@
       <c r="B2" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -28317,21 +28314,21 @@
       <c r="B1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -28340,8 +28337,8 @@
       <c r="B2" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -29061,21 +29058,21 @@
       <c r="B1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -29084,8 +29081,8 @@
       <c r="B2" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -29813,21 +29810,21 @@
       <c r="B1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -29836,8 +29833,8 @@
       <c r="B2" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -30581,21 +30578,21 @@
       <c r="B1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -30604,8 +30601,8 @@
       <c r="B2" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -31373,21 +31370,21 @@
       <c r="B1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -31396,8 +31393,8 @@
       <c r="B2" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -32141,21 +32138,21 @@
       <c r="B1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -32164,8 +32161,8 @@
       <c r="B2" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -32885,21 +32882,21 @@
       <c r="B1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -32908,8 +32905,8 @@
       <c r="B2" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -33709,21 +33706,21 @@
       <c r="B1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -33732,8 +33729,8 @@
       <c r="B2" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -33967,21 +33964,21 @@
       <c r="B1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -33990,8 +33987,8 @@
       <c r="B2" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -34711,21 +34708,21 @@
       <c r="B1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -34734,8 +34731,8 @@
       <c r="B2" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -35471,21 +35468,21 @@
       <c r="B1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -35494,8 +35491,8 @@
       <c r="B2" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -36226,21 +36223,21 @@
       <c r="B1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -36249,8 +36246,8 @@
       <c r="B2" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -36908,21 +36905,21 @@
       <c r="B1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -36931,8 +36928,8 @@
       <c r="B2" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -37660,21 +37657,21 @@
       <c r="B1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -37683,8 +37680,8 @@
       <c r="B2" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -38420,21 +38417,21 @@
       <c r="B1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -38443,8 +38440,8 @@
       <c r="B2" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -39330,21 +39327,21 @@
       <c r="B1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -39353,8 +39350,8 @@
       <c r="B2" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -40216,21 +40213,21 @@
       <c r="B1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -40239,8 +40236,8 @@
       <c r="B2" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -41086,21 +41083,21 @@
       <c r="B1" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -41109,8 +41106,8 @@
       <c r="B2" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -41980,21 +41977,21 @@
       <c r="B1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -42003,8 +42000,8 @@
       <c r="B2" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -42238,21 +42235,21 @@
       <c r="B1" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -42261,8 +42258,8 @@
       <c r="B2" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -43116,21 +43113,21 @@
       <c r="B1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -43139,8 +43136,8 @@
       <c r="B2" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -43906,21 +43903,21 @@
       <c r="B1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -43929,8 +43926,8 @@
       <c r="B2" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -44696,21 +44693,21 @@
       <c r="B1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -44719,8 +44716,8 @@
       <c r="B2" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -45494,21 +45491,21 @@
       <c r="B1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -45517,8 +45514,8 @@
       <c r="B2" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -46292,21 +46289,21 @@
       <c r="B1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -46315,8 +46312,8 @@
       <c r="B2" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -47090,21 +47087,21 @@
       <c r="B1" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -47113,8 +47110,8 @@
       <c r="B2" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -47880,21 +47877,21 @@
       <c r="B1" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -47903,8 +47900,8 @@
       <c r="B2" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -48694,21 +48691,21 @@
       <c r="B1" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -48717,8 +48714,8 @@
       <c r="B2" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -49476,21 +49473,21 @@
       <c r="B1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -49499,8 +49496,8 @@
       <c r="B2" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -50269,21 +50266,21 @@
       <c r="B1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -50292,8 +50289,8 @@
       <c r="B2" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -50535,21 +50532,21 @@
       <c r="B1" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -50558,8 +50555,8 @@
       <c r="B2" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -51408,21 +51405,21 @@
       <c r="B1" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -51431,8 +51428,8 @@
       <c r="B2" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -52128,21 +52125,21 @@
       <c r="B1" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -52151,8 +52148,8 @@
       <c r="B2" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -52923,21 +52920,21 @@
       <c r="B1" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -52946,8 +52943,8 @@
       <c r="B2" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -53742,21 +53739,21 @@
       <c r="B1" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -53765,8 +53762,8 @@
       <c r="B2" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -54537,21 +54534,21 @@
       <c r="B1" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -54560,8 +54557,8 @@
       <c r="B2" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -55332,21 +55329,21 @@
       <c r="B1" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -55355,8 +55352,8 @@
       <c r="B2" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -56127,21 +56124,21 @@
       <c r="B1" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -56150,8 +56147,8 @@
       <c r="B2" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -56938,21 +56935,21 @@
       <c r="B1" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -56961,8 +56958,8 @@
       <c r="B2" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -57781,21 +57778,21 @@
       <c r="B1" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -57804,8 +57801,8 @@
       <c r="B2" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -58584,21 +58581,21 @@
       <c r="B1" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -58607,8 +58604,8 @@
       <c r="B2" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -58842,21 +58839,21 @@
       <c r="B1" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -58865,8 +58862,8 @@
       <c r="B2" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -59637,21 +59634,21 @@
       <c r="B1" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -59660,8 +59657,8 @@
       <c r="B2" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -60464,21 +60461,21 @@
       <c r="B1" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -60487,8 +60484,8 @@
       <c r="B2" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -61299,21 +61296,21 @@
       <c r="B1" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -61322,8 +61319,8 @@
       <c r="B2" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -62150,21 +62147,21 @@
       <c r="B1" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -62173,8 +62170,8 @@
       <c r="B2" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -62977,21 +62974,21 @@
       <c r="B1" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -63000,8 +62997,8 @@
       <c r="B2" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -63812,21 +63809,21 @@
       <c r="B1" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -63835,8 +63832,8 @@
       <c r="B2" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -64615,21 +64612,21 @@
       <c r="B1" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -64638,8 +64635,8 @@
       <c r="B2" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -65418,21 +65415,21 @@
       <c r="B1" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -65441,8 +65438,8 @@
       <c r="B2" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -66221,21 +66218,21 @@
       <c r="B1" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -66244,8 +66241,8 @@
       <c r="B2" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -66960,21 +66957,21 @@
       <c r="B1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -66983,8 +66980,8 @@
       <c r="B2" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -67630,21 +67627,21 @@
       <c r="B1" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -67653,8 +67650,8 @@
       <c r="B2" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -68425,21 +68422,21 @@
       <c r="B1" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -68448,8 +68445,8 @@
       <c r="B2" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -69220,21 +69217,21 @@
       <c r="B1" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -69243,8 +69240,8 @@
       <c r="B2" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -70015,21 +70012,21 @@
       <c r="B1" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -70038,8 +70035,8 @@
       <c r="B2" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -70810,21 +70807,21 @@
       <c r="B1" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -70833,8 +70830,8 @@
       <c r="B2" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -71605,21 +71602,21 @@
       <c r="B1" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -71628,8 +71625,8 @@
       <c r="B2" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -72400,21 +72397,21 @@
       <c r="B1" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -72423,8 +72420,8 @@
       <c r="B2" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -73179,21 +73176,21 @@
       <c r="B1" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -73202,8 +73199,8 @@
       <c r="B2" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -73958,21 +73955,21 @@
       <c r="B1" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -73981,8 +73978,8 @@
       <c r="B2" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -74737,21 +74734,21 @@
       <c r="B1" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -74760,8 +74757,8 @@
       <c r="B2" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -74791,10 +74788,10 @@
       <c r="B3" s="10">
         <v>0.71</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="4" t="s">
         <v>252</v>
       </c>
       <c r="F3" s="7">
@@ -74810,7 +74807,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="30" t="str">
+      <c r="L3" s="4" t="str">
         <f>IF($B$10=$B$11,H3-F3,"")</f>
         <v/>
       </c>
@@ -74838,8 +74835,8 @@
       <c r="B4" s="10">
         <v>0.47</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="7"/>
       <c r="G4" s="5"/>
       <c r="H4" s="7" t="str">
@@ -74849,7 +74846,7 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="30" t="str">
+      <c r="L4" s="4" t="str">
         <f t="shared" ref="L4:L20" si="1">IF($B$10=$B$11,H4-F4,"")</f>
         <v/>
       </c>
@@ -74873,8 +74870,8 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="8"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
       <c r="F5" s="7"/>
       <c r="G5" s="5"/>
       <c r="H5" s="7" t="str">
@@ -74884,7 +74881,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="30" t="str">
+      <c r="L5" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -74908,8 +74905,8 @@
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="8"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
       <c r="F6" s="7"/>
       <c r="G6" s="5"/>
       <c r="H6" s="7" t="str">
@@ -74917,9 +74914,9 @@
         <v/>
       </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="30"/>
+      <c r="J6" s="4"/>
       <c r="K6" s="6"/>
-      <c r="L6" s="30" t="str">
+      <c r="L6" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -74947,8 +74944,8 @@
       <c r="B7" s="8">
         <v>46233</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
       <c r="F7" s="7"/>
       <c r="G7" s="5"/>
       <c r="H7" s="7" t="str">
@@ -74956,9 +74953,9 @@
         <v/>
       </c>
       <c r="I7" s="5"/>
-      <c r="J7" s="30"/>
+      <c r="J7" s="4"/>
       <c r="K7" s="6"/>
-      <c r="L7" s="30" t="str">
+      <c r="L7" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -74986,8 +74983,8 @@
       <c r="B8" s="8">
         <v>46227</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="7"/>
       <c r="G8" s="5"/>
       <c r="H8" s="7" t="str">
@@ -74995,9 +74992,9 @@
         <v/>
       </c>
       <c r="I8" s="5"/>
-      <c r="J8" s="30"/>
+      <c r="J8" s="4"/>
       <c r="K8" s="6"/>
-      <c r="L8" s="30" t="str">
+      <c r="L8" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75023,8 +75020,8 @@
         <v>240</v>
       </c>
       <c r="B9" s="8"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="7"/>
       <c r="G9" s="5"/>
       <c r="H9" s="7" t="str">
@@ -75032,9 +75029,9 @@
         <v/>
       </c>
       <c r="I9" s="5"/>
-      <c r="J9" s="30"/>
+      <c r="J9" s="4"/>
       <c r="K9" s="6"/>
-      <c r="L9" s="30" t="str">
+      <c r="L9" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75063,8 +75060,8 @@
         <f>SUM(G3:G20)</f>
         <v>10.67</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="7"/>
       <c r="G10" s="5"/>
       <c r="H10" s="7" t="str">
@@ -75072,9 +75069,9 @@
         <v/>
       </c>
       <c r="I10" s="5"/>
-      <c r="J10" s="30"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="6"/>
-      <c r="L10" s="30" t="str">
+      <c r="L10" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75103,8 +75100,8 @@
         <f>SUM(I3:I20)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="7"/>
       <c r="G11" s="5"/>
       <c r="H11" s="7" t="str">
@@ -75112,9 +75109,9 @@
         <v/>
       </c>
       <c r="I11" s="5"/>
-      <c r="J11" s="30"/>
+      <c r="J11" s="4"/>
       <c r="K11" s="6"/>
-      <c r="L11" s="30" t="str">
+      <c r="L11" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75143,8 +75140,8 @@
         <f>SUM(J3:J20)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="7"/>
       <c r="G12" s="5"/>
       <c r="H12" s="7" t="str">
@@ -75152,9 +75149,9 @@
         <v/>
       </c>
       <c r="I12" s="5"/>
-      <c r="J12" s="30"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="6"/>
-      <c r="L12" s="30" t="str">
+      <c r="L12" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75183,8 +75180,8 @@
         <f>IF(B10=B11,XIRR(Y3:Z20,W3:X20),"")</f>
         <v/>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="7"/>
       <c r="G13" s="5"/>
       <c r="H13" s="7" t="str">
@@ -75192,9 +75189,9 @@
         <v/>
       </c>
       <c r="I13" s="5"/>
-      <c r="J13" s="30"/>
+      <c r="J13" s="4"/>
       <c r="K13" s="6"/>
-      <c r="L13" s="30" t="str">
+      <c r="L13" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75223,8 +75220,8 @@
         <f>IF(B10=B11,SUMPRODUCT(L3:L20,G3:G20)/SUM(G3:G20),"")</f>
         <v/>
       </c>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
       <c r="F14" s="7"/>
       <c r="G14" s="5"/>
       <c r="H14" s="7" t="str">
@@ -75232,9 +75229,9 @@
         <v/>
       </c>
       <c r="I14" s="5"/>
-      <c r="J14" s="30"/>
+      <c r="J14" s="4"/>
       <c r="K14" s="6"/>
-      <c r="L14" s="30" t="str">
+      <c r="L14" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75256,8 +75253,8 @@
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="7"/>
       <c r="G15" s="5"/>
       <c r="H15" s="7" t="str">
@@ -75265,9 +75262,9 @@
         <v/>
       </c>
       <c r="I15" s="5"/>
-      <c r="J15" s="30"/>
+      <c r="J15" s="4"/>
       <c r="K15" s="6"/>
-      <c r="L15" s="30" t="str">
+      <c r="L15" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75289,8 +75286,8 @@
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="7"/>
       <c r="G16" s="5"/>
       <c r="H16" s="7" t="str">
@@ -75298,9 +75295,9 @@
         <v/>
       </c>
       <c r="I16" s="5"/>
-      <c r="J16" s="30"/>
+      <c r="J16" s="4"/>
       <c r="K16" s="6"/>
-      <c r="L16" s="30" t="str">
+      <c r="L16" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75322,8 +75319,8 @@
       </c>
     </row>
     <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
       <c r="F17" s="7"/>
       <c r="G17" s="5"/>
       <c r="H17" s="7" t="str">
@@ -75331,9 +75328,9 @@
         <v/>
       </c>
       <c r="I17" s="5"/>
-      <c r="J17" s="30"/>
+      <c r="J17" s="4"/>
       <c r="K17" s="6"/>
-      <c r="L17" s="30" t="str">
+      <c r="L17" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75355,8 +75352,8 @@
       </c>
     </row>
     <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="7"/>
       <c r="G18" s="5"/>
       <c r="H18" s="7" t="str">
@@ -75364,9 +75361,9 @@
         <v/>
       </c>
       <c r="I18" s="5"/>
-      <c r="J18" s="30"/>
+      <c r="J18" s="4"/>
       <c r="K18" s="6"/>
-      <c r="L18" s="30" t="str">
+      <c r="L18" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75388,8 +75385,8 @@
       </c>
     </row>
     <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="7"/>
       <c r="G19" s="5"/>
       <c r="H19" s="7" t="str">
@@ -75397,9 +75394,9 @@
         <v/>
       </c>
       <c r="I19" s="5"/>
-      <c r="J19" s="30"/>
+      <c r="J19" s="4"/>
       <c r="K19" s="6"/>
-      <c r="L19" s="30" t="str">
+      <c r="L19" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75421,8 +75418,8 @@
       </c>
     </row>
     <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="7"/>
       <c r="G20" s="5"/>
       <c r="H20" s="7" t="str">
@@ -75430,9 +75427,9 @@
         <v/>
       </c>
       <c r="I20" s="5"/>
-      <c r="J20" s="30"/>
+      <c r="J20" s="4"/>
       <c r="K20" s="6"/>
-      <c r="L20" s="30" t="str">
+      <c r="L20" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -75518,21 +75515,21 @@
       <c r="B1" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -75541,8 +75538,8 @@
       <c r="B2" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
@@ -76248,21 +76245,21 @@
       <c r="B1" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="33"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -76271,8 +76268,8 @@
       <c r="B2" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="3" t="s">
         <v>88</v>
       </c>
